--- a/docs/Mapping_casi_uso/morte/Morte_998_1.xlsx
+++ b/docs/Mapping_casi_uso/morte/Morte_998_1.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="61">
   <si>
     <t>Sezione</t>
   </si>
@@ -129,12 +129,6 @@
   </si>
   <si>
     <t>idAttoCartaceo</t>
-  </si>
-  <si>
-    <t>Atto secretato</t>
-  </si>
-  <si>
-    <t>flagsecretato</t>
   </si>
   <si>
     <t>Evento da annotare</t>
@@ -259,7 +253,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.171875" customWidth="true" bestFit="true"/>
@@ -595,19 +589,19 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>10</v>
@@ -618,16 +612,16 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>44</v>
@@ -641,7 +635,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>45</v>
@@ -650,7 +644,7 @@
         <v>13</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>46</v>
@@ -664,7 +658,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>47</v>
@@ -673,7 +667,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>48</v>
@@ -687,7 +681,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>49</v>
@@ -696,7 +690,7 @@
         <v>13</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>50</v>
@@ -710,7 +704,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>51</v>
@@ -719,10 +713,10 @@
         <v>13</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>10</v>
@@ -733,19 +727,19 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>10</v>
@@ -756,7 +750,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>54</v>
@@ -765,10 +759,10 @@
         <v>13</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>10</v>
@@ -779,19 +773,19 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>10</v>
@@ -802,7 +796,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>57</v>
@@ -811,7 +805,7 @@
         <v>13</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>58</v>
@@ -825,13 +819,13 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>17</v>
@@ -843,29 +837,6 @@
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26" s="2" t="s">
         <v>19</v>
       </c>
     </row>
